--- a/planning.xlsx
+++ b/planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\prj\fhu\vmback\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2A3C93-AFDE-434F-8FAB-94276AA40653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1D29D1-B013-4968-BE8C-6CB3A511D7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1770" yWindow="1770" windowWidth="23175" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -586,6 +586,10 @@
         <f>40+500</f>
         <v>540</v>
       </c>
+      <c r="G4" s="1">
+        <f>$C4</f>
+        <v>540</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -595,6 +599,10 @@
         <v>46</v>
       </c>
       <c r="C5" s="1">
+        <v>40</v>
+      </c>
+      <c r="G5" s="1">
+        <f>$C5</f>
         <v>40</v>
       </c>
     </row>
@@ -863,7 +871,7 @@
       </c>
       <c r="G26" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="H26" s="1">
         <f t="shared" si="0"/>
@@ -875,7 +883,7 @@
       </c>
       <c r="J26" s="1">
         <f>SUM(D26:I26)</f>
-        <v>3510</v>
+        <v>4090</v>
       </c>
     </row>
   </sheetData>

--- a/planning.xlsx
+++ b/planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\prj\fhu\vmback\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C1D29D1-B013-4968-BE8C-6CB3A511D7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A31739-31BB-4585-808A-52F9105B16B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="1770" windowWidth="23175" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2115" yWindow="2115" windowWidth="23175" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>VM name</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>f7d0410a-c975-a022-3475-1b4d592e2fab</t>
+  </si>
+  <si>
+    <t>thu</t>
   </si>
 </sst>
 </file>
@@ -515,15 +518,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="9.140625" style="1"/>
+    <col min="3" max="10" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -549,10 +552,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -562,8 +568,12 @@
       <c r="C2" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I2" s="1">
+        <f>$C2</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -575,7 +585,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -591,7 +601,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -606,7 +616,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -622,7 +632,7 @@
         <v>2890</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -633,8 +643,12 @@
         <f>10+10</f>
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I7" s="1">
+        <f>$C7</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -644,8 +658,12 @@
       <c r="C8" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I8" s="1">
+        <f>$C8</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -656,7 +674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -667,7 +685,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -678,8 +696,12 @@
         <f>20+100</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I11" s="1">
+        <f>$C11</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -690,8 +712,12 @@
         <f>20+50</f>
         <v>70</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I12" s="1">
+        <f>$C12</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -702,8 +728,12 @@
         <f>40+100</f>
         <v>140</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I13" s="1">
+        <f>$C13</f>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -718,7 +748,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -729,8 +759,12 @@
         <f>20+100</f>
         <v>120</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="1">
+        <f>$C15</f>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -742,7 +776,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>51</v>
       </c>
@@ -753,7 +787,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -764,8 +798,12 @@
         <f>20+20+20</f>
         <v>60</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I18" s="1">
+        <f>$C18</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -776,7 +814,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -787,7 +825,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -798,7 +836,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -810,7 +848,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -821,7 +859,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -837,7 +875,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -852,13 +890,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C26" s="1">
         <f>SUM(C2:C25)</f>
         <v>6850</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" ref="D26:I26" si="0">SUM(D2:D25)</f>
+        <f t="shared" ref="D26:J26" si="0">SUM(D2:D25)</f>
         <v>2930</v>
       </c>
       <c r="E26" s="1">
@@ -879,15 +917,19 @@
       </c>
       <c r="I26" s="1">
         <f t="shared" si="0"/>
+        <v>610</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="1">
-        <f>SUM(D26:I26)</f>
-        <v>4090</v>
+      <c r="K26" s="1">
+        <f>SUM(D26:J26)</f>
+        <v>4700</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I25">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
     <sortCondition ref="A2:A25"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/planning.xlsx
+++ b/planning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\prj\fhu\vmback\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A31739-31BB-4585-808A-52F9105B16B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277A2815-478F-46C8-BF1E-1425E0423F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2115" yWindow="2115" windowWidth="23175" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -700,6 +700,10 @@
         <f>$C11</f>
         <v>120</v>
       </c>
+      <c r="J11" s="1">
+        <f>$C11</f>
+        <v>120</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -716,6 +720,10 @@
         <f>$C12</f>
         <v>70</v>
       </c>
+      <c r="J12" s="1">
+        <f>$C12</f>
+        <v>70</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -732,6 +740,10 @@
         <f>$C13</f>
         <v>140</v>
       </c>
+      <c r="J13" s="1">
+        <f>$C13</f>
+        <v>140</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -747,6 +759,10 @@
         <f>$C14</f>
         <v>40</v>
       </c>
+      <c r="J14" s="1">
+        <f>$C14</f>
+        <v>40</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -775,6 +791,10 @@
         <f>40+100</f>
         <v>140</v>
       </c>
+      <c r="J16" s="1">
+        <f>$C16</f>
+        <v>140</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -786,6 +806,10 @@
       <c r="C17" s="1">
         <v>40</v>
       </c>
+      <c r="J17" s="1">
+        <f>$C17</f>
+        <v>40</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -813,6 +837,10 @@
       <c r="C19" s="1">
         <v>40</v>
       </c>
+      <c r="J19" s="1">
+        <f t="shared" ref="J19:J23" si="0">$C19</f>
+        <v>40</v>
+      </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -824,6 +852,10 @@
       <c r="C20" s="1">
         <v>40</v>
       </c>
+      <c r="J20" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -835,6 +867,10 @@
       <c r="C21" s="1">
         <v>100</v>
       </c>
+      <c r="J21" s="1">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
@@ -856,6 +892,10 @@
         <v>24</v>
       </c>
       <c r="C23" s="1">
+        <v>20</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
@@ -896,36 +936,36 @@
         <v>6850</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" ref="D26:J26" si="0">SUM(D2:D25)</f>
+        <f t="shared" ref="D26:J26" si="1">SUM(D2:D25)</f>
         <v>2930</v>
       </c>
       <c r="E26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>580</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>580</v>
       </c>
       <c r="H26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>610</v>
       </c>
       <c r="J26" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>750</v>
       </c>
       <c r="K26" s="1">
         <f>SUM(D26:J26)</f>
-        <v>4700</v>
+        <v>5450</v>
       </c>
     </row>
   </sheetData>
